--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488019_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488019_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2818</v>
+        <v>1.8298</v>
       </c>
       <c r="E2" t="n">
-        <v>1.3335</v>
+        <v>2.5165</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.0517</v>
+        <v>-0.6867</v>
       </c>
       <c r="G2" t="n">
         <v>2.8819</v>
@@ -610,13 +610,13 @@
         <v>0.9911</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.9261</v>
+        <v>-0.3781</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.1855</v>
+        <v>-0.0026</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.7405</v>
+        <v>-0.3755</v>
       </c>
       <c r="V2" t="n">
         <v>-0.674</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. SIMON DIAZ</t>
+          <t>N. PENA BANOS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1536</v>
+        <v>0.2845</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.2648</v>
+        <v>-0.9657</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4184</v>
+        <v>1.2502</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.4273</v>
+        <v>-0.5568</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.0222</v>
+        <v>-2.2461</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5949</v>
+        <v>1.6893</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.2575</v>
+        <v>0.6952</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.2977</v>
+        <v>-1.9163</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0402</v>
+        <v>2.6115</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8303</v>
+        <v>-1.252</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2756</v>
+        <v>-0.3298</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5547</v>
+        <v>-0.9223</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5947</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R3" t="n">
         <v>0.5947</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5193</v>
+        <v>-0.1101</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0072</v>
+        <v>-0.6698</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5266</v>
+        <v>0.5597</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.5331</v>
+        <v>1.3479</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5331</v>
+        <v>1.3479</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>N. PENA BANOS</t>
+          <t>A. SIMON DIAZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1245</v>
+        <v>-0.5108</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.2942</v>
+        <v>-1.508</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4187</v>
+        <v>0.9972</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.5568</v>
+        <v>-0.4273</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.2461</v>
+        <v>-1.0222</v>
       </c>
       <c r="I4" t="n">
-        <v>1.6893</v>
+        <v>0.5949</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6952</v>
+        <v>-1.2575</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.9163</v>
+        <v>-1.2977</v>
       </c>
       <c r="L4" t="n">
-        <v>2.6115</v>
+        <v>0.0402</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.252</v>
+        <v>0.8303</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3298</v>
+        <v>0.2756</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.9223</v>
+        <v>0.5547</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.3964</v>
+        <v>0.5947</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0.5947</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2702</v>
+        <v>-0.145</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9984</v>
+        <v>-0.2505</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7282</v>
+        <v>0.1054</v>
       </c>
       <c r="V4" t="n">
-        <v>1.3479</v>
+        <v>-0.5331</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.3479</v>
+        <v>-0.5331</v>
       </c>
     </row>
     <row r="5">
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.092</v>
+        <v>-0.7864</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.0579</v>
+        <v>-0.7523</v>
       </c>
       <c r="F5" t="n">
         <v>-0.0341</v>
@@ -844,10 +844,10 @@
         <v>0.5947</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8774</v>
+        <v>-0.5717</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.301</v>
+        <v>0.0047</v>
       </c>
       <c r="U5" t="n">
         <v>-0.5764</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.4042</v>
+        <v>-0.8677</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6916</v>
+        <v>1.0596</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.0958</v>
+        <v>-1.9274</v>
       </c>
       <c r="G6" t="n">
         <v>0.1898</v>
@@ -922,13 +922,13 @@
         <v>0.3964</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7833</v>
+        <v>-0.2468</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.624</v>
+        <v>-0.256</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1593</v>
+        <v>0.0091</v>
       </c>
       <c r="V6" t="n">
         <v>-1.2071</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>V. STRUKOV STRUKOV</t>
+          <t>A. GARCIA MONTELLANO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.5732</v>
+        <v>-1.7394</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.313</v>
+        <v>-0.3475</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.2602</v>
+        <v>-1.3919</v>
       </c>
       <c r="G7" t="n">
-        <v>-6.526</v>
+        <v>-1.1052</v>
       </c>
       <c r="H7" t="n">
-        <v>-4.7849</v>
+        <v>1.7033</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.7411</v>
+        <v>-2.8085</v>
       </c>
       <c r="J7" t="n">
-        <v>-4.2765</v>
+        <v>0.0655</v>
       </c>
       <c r="K7" t="n">
-        <v>-4.3971</v>
+        <v>1.4199</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1205</v>
+        <v>-1.3544</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.2495</v>
+        <v>-1.1708</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3879</v>
+        <v>0.2834</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.8617</v>
+        <v>-1.4542</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.1893</v>
+        <v>0.5947</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7929</v>
+        <v>0.5947</v>
       </c>
       <c r="S7" t="n">
-        <v>6.7457</v>
+        <v>0.5818</v>
       </c>
       <c r="T7" t="n">
-        <v>5.6792</v>
+        <v>-0.076</v>
       </c>
       <c r="U7" t="n">
-        <v>1.0665</v>
+        <v>0.6578000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.6036</v>
+        <v>-1.8107</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2666</v>
+        <v>-0.337</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.8701</v>
+        <v>-1.4737</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. GARCIA MONTELLANO</t>
+          <t>J. REVUELTAS PAREJA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.1417</v>
+        <v>-3.4127</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7779</v>
+        <v>-1.5542</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.3638</v>
+        <v>-1.8585</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.1052</v>
+        <v>-2.0453</v>
       </c>
       <c r="H8" t="n">
-        <v>1.7033</v>
+        <v>-4.1787</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.8085</v>
+        <v>2.1333</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0655</v>
+        <v>-1.3427</v>
       </c>
       <c r="K8" t="n">
-        <v>1.4199</v>
+        <v>-3.0457</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.3544</v>
+        <v>1.703</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.1708</v>
+        <v>-0.7027</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2834</v>
+        <v>-1.1329</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.4542</v>
+        <v>0.4303</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5947</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5947</v>
+        <v>0.7929</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1795</v>
+        <v>-0.636</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5064</v>
+        <v>-0.4275</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6859</v>
+        <v>-0.2085</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.8107</v>
+        <v>-0.5331</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.337</v>
+        <v>1.2071</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.4737</v>
+        <v>-1.7403</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. REVUELTAS PAREJA</t>
+          <t>D. ABOY MARQUEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.813</v>
+        <v>-3.7904</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7579</v>
+        <v>-0.3095</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.055</v>
+        <v>-3.4809</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.0453</v>
+        <v>-2.9104</v>
       </c>
       <c r="H9" t="n">
-        <v>-4.1787</v>
+        <v>0.1545</v>
       </c>
       <c r="I9" t="n">
-        <v>2.1333</v>
+        <v>-3.0649</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.3427</v>
+        <v>-0.5115</v>
       </c>
       <c r="K9" t="n">
-        <v>-3.0457</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>1.703</v>
+        <v>-1.1975</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7027</v>
+        <v>-2.3989</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.1329</v>
+        <v>-0.5315</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4303</v>
+        <v>-1.8674</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1982</v>
+        <v>0.5947</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7929</v>
+        <v>0.5947</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0362</v>
+        <v>0.3359</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6312</v>
+        <v>0.202</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.405</v>
+        <v>0.1339</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.5331</v>
+        <v>-1.8107</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.7403</v>
+        <v>-1.8107</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. ABOY MARQUEZ</t>
+          <t>E. LALI VICENTE UCHUATE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.724</v>
+        <v>-4.6745</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.1868</v>
+        <v>-3.5957</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.5371</v>
+        <v>-1.0788</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.9104</v>
+        <v>-3.3599</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1545</v>
+        <v>-0.6068</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.0649</v>
+        <v>-2.7531</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.5115</v>
+        <v>-1.52</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.3165</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.1975</v>
+        <v>-1.8365</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.3989</v>
+        <v>-1.8399</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5315</v>
+        <v>-0.9233</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.8674</v>
+        <v>-0.9166</v>
       </c>
       <c r="P10" t="n">
-        <v>0.5947</v>
+        <v>-1.784</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-2.9733</v>
       </c>
       <c r="R10" t="n">
-        <v>0.5947</v>
+        <v>1.1893</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5976</v>
+        <v>0.2029</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6753</v>
+        <v>0.3646</v>
       </c>
       <c r="U10" t="n">
-        <v>0.07779999999999999</v>
+        <v>-0.1617</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.8107</v>
+        <v>0.2666</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.5331</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.8107</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E. LALI VICENTE UCHUATE</t>
+          <t>V. STRUKOV STRUKOV</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.2047</v>
+        <v>-5.5712</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.9013</v>
+        <v>-3.9179</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.3034</v>
+        <v>-1.6533</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.3599</v>
+        <v>-6.526</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.6068</v>
+        <v>-4.7849</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.7531</v>
+        <v>-1.7411</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.52</v>
+        <v>-4.2765</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3165</v>
+        <v>-4.3971</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.8365</v>
+        <v>0.1205</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.8399</v>
+        <v>-2.2495</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.9233</v>
+        <v>-0.3879</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.9166</v>
+        <v>-1.8617</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.784</v>
+        <v>-1.1893</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.9733</v>
+        <v>-1.9822</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1893</v>
+        <v>0.7929</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3274</v>
+        <v>2.7477</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0589</v>
+        <v>2.0743</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3863</v>
+        <v>0.6734</v>
       </c>
       <c r="V11" t="n">
+        <v>-0.6036</v>
+      </c>
+      <c r="W11" t="n">
         <v>0.2666</v>
       </c>
-      <c r="W11" t="n">
-        <v>0.5331</v>
-      </c>
       <c r="X11" t="n">
-        <v>-0.2666</v>
+        <v>-0.8701</v>
       </c>
     </row>
     <row r="12">
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-9.727600000000001</v>
+        <v>-9.2577</v>
       </c>
       <c r="E12" t="n">
-        <v>-9.652900000000001</v>
+        <v>-9.183</v>
       </c>
       <c r="F12" t="n">
         <v>-0.0747</v>
@@ -1390,10 +1390,10 @@
         <v>0.7929</v>
       </c>
       <c r="S12" t="n">
-        <v>0.8884</v>
+        <v>1.3583</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1837</v>
+        <v>0.6536</v>
       </c>
       <c r="U12" t="n">
         <v>0.7046</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-29.1205</v>
+        <v>-28.4965</v>
       </c>
       <c r="E13" t="n">
-        <v>-19.1816</v>
+        <v>-18.5577</v>
       </c>
       <c r="F13" t="n">
-        <v>-9.938700000000001</v>
+        <v>-9.938899999999999</v>
       </c>
       <c r="G13" t="n">
         <v>-17.8819</v>
@@ -1438,16 +1438,16 @@
         <v>-14.5719</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.3101</v>
+        <v>-3.310099999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>-6.449100000000001</v>
+        <v>-6.4491</v>
       </c>
       <c r="K13" t="n">
         <v>-10.3243</v>
       </c>
       <c r="L13" t="n">
-        <v>3.875200000000001</v>
+        <v>3.8752</v>
       </c>
       <c r="M13" t="n">
         <v>-11.4329</v>
@@ -1465,16 +1465,16 @@
         <v>-15.8577</v>
       </c>
       <c r="R13" t="n">
-        <v>7.929</v>
+        <v>7.929000000000001</v>
       </c>
       <c r="S13" t="n">
-        <v>2.5147</v>
+        <v>3.1389</v>
       </c>
       <c r="T13" t="n">
-        <v>0.9928000000000003</v>
+        <v>1.6168</v>
       </c>
       <c r="U13" t="n">
-        <v>1.5221</v>
+        <v>1.5218</v>
       </c>
       <c r="V13" t="n">
         <v>-5.8243</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.987</v>
+        <v>5.6148</v>
       </c>
       <c r="E14" t="n">
-        <v>4.2677</v>
+        <v>4.064</v>
       </c>
       <c r="F14" t="n">
-        <v>1.7193</v>
+        <v>1.5509</v>
       </c>
       <c r="G14" t="n">
         <v>2.7249</v>
@@ -1546,13 +1546,13 @@
         <v>1.1893</v>
       </c>
       <c r="S14" t="n">
-        <v>1.6607</v>
+        <v>1.2885</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3599</v>
+        <v>0.1562</v>
       </c>
       <c r="U14" t="n">
-        <v>1.3008</v>
+        <v>1.1323</v>
       </c>
       <c r="V14" t="n">
         <v>1.4033</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.4932</v>
+        <v>5.0117</v>
       </c>
       <c r="E15" t="n">
-        <v>1.344</v>
+        <v>1.4458</v>
       </c>
       <c r="F15" t="n">
-        <v>3.1492</v>
+        <v>3.5658</v>
       </c>
       <c r="G15" t="n">
         <v>3.2567</v>
@@ -1624,13 +1624,13 @@
         <v>2.3787</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.7437</v>
+        <v>-1.2252</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3082</v>
+        <v>-0.2063</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.4355</v>
+        <v>-1.0189</v>
       </c>
       <c r="V15" t="n">
         <v>0.7997</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.6802</v>
+        <v>4.7361</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2406</v>
+        <v>0.8518</v>
       </c>
       <c r="F16" t="n">
-        <v>3.4396</v>
+        <v>3.8843</v>
       </c>
       <c r="G16" t="n">
         <v>1.6768</v>
@@ -1702,13 +1702,13 @@
         <v>2.3787</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.5913</v>
+        <v>-1.5354</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.1745</v>
+        <v>-0.5633</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.4168</v>
+        <v>-0.9721</v>
       </c>
       <c r="V16" t="n">
         <v>2.4142</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. DIMITROV KOLEV</t>
+          <t>A. BUZZO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.6474</v>
+        <v>3.3554</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0345</v>
+        <v>1.8844</v>
       </c>
       <c r="F17" t="n">
-        <v>1.6129</v>
+        <v>1.471</v>
       </c>
       <c r="G17" t="n">
-        <v>1.4362</v>
+        <v>3.4334</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7972</v>
+        <v>1.6407</v>
       </c>
       <c r="I17" t="n">
-        <v>0.639</v>
+        <v>1.7927</v>
       </c>
       <c r="J17" t="n">
-        <v>1.1335</v>
+        <v>2.2652</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3701</v>
+        <v>1.0158</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7634</v>
+        <v>1.2494</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3027</v>
+        <v>1.1683</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4271</v>
+        <v>0.625</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1244</v>
+        <v>0.5433</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9911</v>
+        <v>1.1893</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.1982</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9911</v>
+        <v>1.3876</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8831</v>
+        <v>-0.7342</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2975</v>
+        <v>-0.1825</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5856</v>
+        <v>-0.5517</v>
       </c>
       <c r="V17" t="n">
-        <v>0.337</v>
+        <v>-0.5331</v>
       </c>
       <c r="W17" t="n">
-        <v>0.6036</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2666</v>
+        <v>-0.5331</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.3363</v>
+        <v>2.7813</v>
       </c>
       <c r="E18" t="n">
-        <v>2.9415</v>
+        <v>2.3303</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3948</v>
+        <v>0.451</v>
       </c>
       <c r="G18" t="n">
         <v>2.9368</v>
@@ -1858,13 +1858,13 @@
         <v>0.7929</v>
       </c>
       <c r="S18" t="n">
-        <v>1.3223</v>
+        <v>0.7672</v>
       </c>
       <c r="T18" t="n">
-        <v>0.7343</v>
+        <v>0.1231</v>
       </c>
       <c r="U18" t="n">
-        <v>0.588</v>
+        <v>0.6441</v>
       </c>
       <c r="V18" t="n">
         <v>0.2666</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. BUZZO</t>
+          <t>J. CEBRIAN ROSAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.0218</v>
+        <v>2.6921</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5788</v>
+        <v>0.161</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4429</v>
+        <v>2.5311</v>
       </c>
       <c r="G19" t="n">
-        <v>3.4334</v>
+        <v>2.1542</v>
       </c>
       <c r="H19" t="n">
-        <v>1.6407</v>
+        <v>1.6777</v>
       </c>
       <c r="I19" t="n">
-        <v>1.7927</v>
+        <v>0.4764</v>
       </c>
       <c r="J19" t="n">
-        <v>2.2652</v>
+        <v>0.7086</v>
       </c>
       <c r="K19" t="n">
-        <v>1.0158</v>
+        <v>0.7811</v>
       </c>
       <c r="L19" t="n">
-        <v>1.2494</v>
+        <v>-0.0726</v>
       </c>
       <c r="M19" t="n">
-        <v>1.1683</v>
+        <v>1.4456</v>
       </c>
       <c r="N19" t="n">
-        <v>0.625</v>
+        <v>0.8966</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5433</v>
+        <v>0.549</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1893</v>
+        <v>0.3964</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.1982</v>
+        <v>-1.1893</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3876</v>
+        <v>1.5858</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0679</v>
+        <v>-0.7287</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4881</v>
+        <v>-0.2284</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5797</v>
+        <v>-0.5003</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.5331</v>
+        <v>0.8701</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.8701</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5331</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C. MORTELLARO</t>
+          <t>I. DIMITROV KOLEV</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.9924</v>
+        <v>2.5412</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6864</v>
+        <v>1.3215</v>
       </c>
       <c r="F20" t="n">
-        <v>3.6788</v>
+        <v>1.2198</v>
       </c>
       <c r="G20" t="n">
-        <v>2.1394</v>
+        <v>1.4362</v>
       </c>
       <c r="H20" t="n">
-        <v>2.8608</v>
+        <v>0.7972</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.7214</v>
+        <v>0.639</v>
       </c>
       <c r="J20" t="n">
-        <v>1.1561</v>
+        <v>1.1335</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9553</v>
+        <v>0.3701</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2009</v>
+        <v>0.7634</v>
       </c>
       <c r="M20" t="n">
-        <v>0.9832</v>
+        <v>0.3027</v>
       </c>
       <c r="N20" t="n">
-        <v>1.9055</v>
+        <v>0.4271</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.9223</v>
+        <v>-0.1244</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.1982</v>
+        <v>0.9911</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.1805</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.9822</v>
+        <v>0.9911</v>
       </c>
       <c r="S20" t="n">
-        <v>1.4586</v>
+        <v>-0.223</v>
       </c>
       <c r="T20" t="n">
-        <v>0.7453</v>
+        <v>-0.4156</v>
       </c>
       <c r="U20" t="n">
-        <v>0.7133</v>
+        <v>0.1925</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.4074</v>
+        <v>0.337</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.4074</v>
+        <v>0.6036</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. CEBRIAN ROSAS</t>
+          <t>C. MORTELLARO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2.0423</v>
+        <v>2.0926</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.3484</v>
+        <v>-0.992</v>
       </c>
       <c r="F21" t="n">
-        <v>2.3907</v>
+        <v>3.0846</v>
       </c>
       <c r="G21" t="n">
-        <v>2.1542</v>
+        <v>2.1394</v>
       </c>
       <c r="H21" t="n">
-        <v>1.6777</v>
+        <v>2.8608</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4764</v>
+        <v>-0.7214</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7086</v>
+        <v>1.1561</v>
       </c>
       <c r="K21" t="n">
-        <v>0.7811</v>
+        <v>0.9553</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.0726</v>
+        <v>0.2009</v>
       </c>
       <c r="M21" t="n">
-        <v>1.4456</v>
+        <v>0.9832</v>
       </c>
       <c r="N21" t="n">
-        <v>0.8966</v>
+        <v>1.9055</v>
       </c>
       <c r="O21" t="n">
-        <v>0.549</v>
+        <v>-0.9223</v>
       </c>
       <c r="P21" t="n">
-        <v>0.3964</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1893</v>
+        <v>-2.1805</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5858</v>
+        <v>1.9822</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.3784</v>
+        <v>0.5588</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7377</v>
+        <v>0.4397</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6407</v>
+        <v>0.1191</v>
       </c>
       <c r="V21" t="n">
-        <v>0.8701</v>
+        <v>-0.4074</v>
       </c>
       <c r="W21" t="n">
-        <v>0.8701</v>
+        <v>-0.4074</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>F. LASCORZ RIVARES</t>
+          <t>J. AGUERA ZEA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2817</v>
+        <v>0.5748</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.0649</v>
+        <v>-0.2111</v>
       </c>
       <c r="F24" t="n">
-        <v>1.3466</v>
+        <v>0.7859</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1053</v>
+        <v>-3.2382</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.2677</v>
+        <v>0.4138</v>
       </c>
       <c r="I24" t="n">
-        <v>0.373</v>
+        <v>-3.652</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.1913</v>
+        <v>-2.5277</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.9547</v>
+        <v>0.0605</v>
       </c>
       <c r="L24" t="n">
-        <v>0.7634</v>
+        <v>-2.5882</v>
       </c>
       <c r="M24" t="n">
-        <v>0.2966</v>
+        <v>-0.7105</v>
       </c>
       <c r="N24" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.3533</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.3904</v>
+        <v>-1.0638</v>
       </c>
       <c r="P24" t="n">
-        <v>0.3964</v>
+        <v>0.7929</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3876</v>
+        <v>0.7929</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0466</v>
+        <v>0.2689</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1176</v>
+        <v>-0.3642</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.07099999999999999</v>
+        <v>0.6331</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.2666</v>
+        <v>2.7512</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>2.6808</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.2666</v>
+        <v>0.0704</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>J. AGUERA ZEA</t>
+          <t>F. LASCORZ RIVARES</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2153</v>
+        <v>0.0277</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.7204</v>
+        <v>-1.3705</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5051</v>
+        <v>1.3982</v>
       </c>
       <c r="G25" t="n">
-        <v>-3.2382</v>
+        <v>0.1053</v>
       </c>
       <c r="H25" t="n">
-        <v>0.4138</v>
+        <v>-0.2677</v>
       </c>
       <c r="I25" t="n">
-        <v>-3.652</v>
+        <v>0.373</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.5277</v>
+        <v>-0.1913</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0605</v>
+        <v>-0.9547</v>
       </c>
       <c r="L25" t="n">
-        <v>-2.5882</v>
+        <v>0.7634</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.7105</v>
+        <v>0.2966</v>
       </c>
       <c r="N25" t="n">
-        <v>0.3533</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.0638</v>
+        <v>-0.3904</v>
       </c>
       <c r="P25" t="n">
-        <v>0.7929</v>
+        <v>0.3964</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R25" t="n">
-        <v>0.7929</v>
+        <v>1.3876</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.5212</v>
+        <v>-0.2074</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.8736</v>
+        <v>-0.1881</v>
       </c>
       <c r="U25" t="n">
-        <v>0.3523</v>
+        <v>-0.0194</v>
       </c>
       <c r="V25" t="n">
-        <v>2.7512</v>
+        <v>-0.2666</v>
       </c>
       <c r="W25" t="n">
-        <v>2.6808</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0.0704</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.2573</v>
+        <v>-1.7388</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.7589</v>
+        <v>-1.657</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.4984</v>
+        <v>-0.0818</v>
       </c>
       <c r="G26" t="n">
         <v>-0.8541</v>
@@ -2482,13 +2482,13 @@
         <v>0.9911</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.5836</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.1944</v>
+        <v>-0.0926</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.3892</v>
+        <v>0.0274</v>
       </c>
       <c r="V26" t="n">
         <v>-1.8107</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>29.1203</v>
+        <v>29.7995</v>
       </c>
       <c r="E27" t="n">
-        <v>9.938699999999999</v>
+        <v>9.938800000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>19.1815</v>
+        <v>19.8608</v>
       </c>
       <c r="G27" t="n">
         <v>17.882</v>
@@ -2539,7 +2539,7 @@
         <v>4.2476</v>
       </c>
       <c r="L27" t="n">
-        <v>7.185500000000001</v>
+        <v>7.1855</v>
       </c>
       <c r="M27" t="n">
         <v>6.4491</v>
@@ -2560,16 +2560,16 @@
         <v>15.8579</v>
       </c>
       <c r="S27" t="n">
-        <v>-2.5148</v>
+        <v>-1.8357</v>
       </c>
       <c r="T27" t="n">
-        <v>-1.5219</v>
+        <v>-1.522</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.9929000000000001</v>
+        <v>-0.3138999999999998</v>
       </c>
       <c r="V27" t="n">
-        <v>5.8243</v>
+        <v>5.824299999999999</v>
       </c>
       <c r="W27" t="n">
         <v>7.9569</v>
